--- a/data/b2_centro/B2 Centro 03-2026.xlsx
+++ b/data/b2_centro/B2 Centro 03-2026.xlsx
@@ -4918,61 +4918,61 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>681.37</v>
+        <v>651.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>78582.49000000001</v>
+        <v>2322.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1454.06</v>
+        <v>79048.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46088</v>
+        <v>46087</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>4014.13</v>
+        <v>2110.67</v>
       </c>
     </row>
     <row r="6">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>5704.13</v>
+        <v>5598.95</v>
       </c>
     </row>
     <row r="7">
@@ -4999,16 +4999,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2577.38</v>
+        <v>2851.27</v>
       </c>
     </row>
     <row r="8">
@@ -5062,25 +5062,25 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1951.85</v>
+        <v>1690.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>15302.46</v>
+        <v>4701.37</v>
       </c>
     </row>
     <row r="12">
@@ -5089,16 +5089,16 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>4125.49</v>
+        <v>15862.18</v>
       </c>
     </row>
     <row r="13">
@@ -5107,34 +5107,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>5551.51</v>
+        <v>4103.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>3338.22</v>
+        <v>5915.47</v>
       </c>
     </row>
     <row r="15">
@@ -5170,12 +5170,12 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>27225.81</v>
+        <v>27083.55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5184,11 +5184,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>2135.13</v>
+        <v>1394.63</v>
       </c>
     </row>
     <row r="18">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>5492.51</v>
+        <v>5966.17</v>
       </c>
     </row>
     <row r="19">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>5787.85</v>
+        <v>6130.41</v>
       </c>
     </row>
     <row r="20">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1609.29</v>
+        <v>1459.77</v>
       </c>
     </row>
   </sheetData>
